--- a/fhir/core/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/fhir/core/StructureDefinition-dk-core-basic-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.5.0</t>
+    <t>3.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T17:27:08+01:00</t>
+    <t>2026-03-11T23:16:27+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2629,7 +2629,7 @@
     <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="209.01171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>

--- a/fhir/core/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/fhir/core/StructureDefinition-dk-core-basic-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.6.0</t>
+    <t>3.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T23:16:27+01:00</t>
+    <t>2026-05-30T15:25:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2629,7 +2629,7 @@
     <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="209.01171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
